--- a/examples/Agilent/ใบสั่งงาน JOB 6.xlsx
+++ b/examples/Agilent/ใบสั่งงาน JOB 6.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ffa44234d445c58/Contract mfg/Agilent/A1 ใบสั่งงาน/ใบสั่งงานฉบับแก้ไข/ฟอร์มใบสั่งงาน/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vatska\software\examples\Agilent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{95BB05E0-B983-49C5-982A-7F2F4B51C454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21A30344-3EF3-4740-A209-853EED5D537A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B352085-9521-43A4-9A4A-1FD9D7850AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="958" activeTab="2" xr2:uid="{4F180DBB-2D27-44A5-BB20-72766F3B0AE8}"/>
+    <workbookView xWindow="-28800" yWindow="480" windowWidth="28800" windowHeight="15150" tabRatio="958" xr2:uid="{4F180DBB-2D27-44A5-BB20-72766F3B0AE8}"/>
   </bookViews>
   <sheets>
-    <sheet name="ใบงาน Agilent_JOBB6" sheetId="10" r:id="rId1"/>
+    <sheet name="ใบงาน Agilent_JOB 6" sheetId="10" r:id="rId1"/>
     <sheet name="A2-QCถุง" sheetId="11" r:id="rId2"/>
     <sheet name="P2-QC กล่อง" sheetId="12" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'ใบงาน Agilent_JOBB6'!$A$1:$N$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'ใบงาน Agilent_JOB 6'!$A$1:$N$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1159,7 +1158,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1355,362 +1354,363 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="12" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1816,9 +1816,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1289050</xdr:colOff>
+      <xdr:colOff>1287145</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>28574</xdr:rowOff>
+      <xdr:rowOff>26669</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2135,9 +2135,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2175,7 +2175,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2281,7 +2281,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2423,7 +2423,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2432,13 +2432,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{819229A0-69E4-4460-8852-75992D2CEC43}">
   <dimension ref="A1:O64"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="11.4"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="2"/>
     <col min="2" max="2" width="21.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="26.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.86328125" style="2" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" style="2" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.6640625" style="1" customWidth="1"/>
@@ -2452,83 +2452,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="104"/>
-      <c r="M1" s="104"/>
-    </row>
-    <row r="2" spans="1:15" ht="11.65" customHeight="1">
-      <c r="A2" s="104"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104"/>
-      <c r="J2" s="104"/>
-      <c r="K2" s="104"/>
-      <c r="L2" s="104"/>
-      <c r="M2" s="104"/>
-    </row>
-    <row r="3" spans="1:15" ht="11.65" customHeight="1">
-      <c r="A3" s="104"/>
-      <c r="B3" s="104"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104"/>
-      <c r="K3" s="104"/>
-      <c r="L3" s="104"/>
-      <c r="M3" s="104"/>
-    </row>
-    <row r="4" spans="1:15" ht="11.65" customHeight="1">
-      <c r="A4" s="104"/>
-      <c r="B4" s="104"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="104"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="104"/>
-      <c r="L4" s="104"/>
-      <c r="M4" s="104"/>
-    </row>
-    <row r="5" spans="1:15" ht="11.65" customHeight="1">
-      <c r="A5" s="104"/>
-      <c r="B5" s="104"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
-      <c r="M5" s="104"/>
-    </row>
-    <row r="6" spans="1:15" ht="22.5">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+    </row>
+    <row r="2" spans="1:15" ht="11.7" customHeight="1">
+      <c r="A2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
+    </row>
+    <row r="3" spans="1:15" ht="11.7" customHeight="1">
+      <c r="A3" s="76"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+    </row>
+    <row r="4" spans="1:15" ht="11.7" customHeight="1">
+      <c r="A4" s="76"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
+    </row>
+    <row r="5" spans="1:15" ht="11.7" customHeight="1">
+      <c r="A5" s="76"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+    </row>
+    <row r="6" spans="1:15" ht="22.8">
       <c r="A6" s="4" t="s">
         <v>36</v>
       </c>
@@ -2541,7 +2541,9 @@
       <c r="A7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="45"/>
+      <c r="B7" s="75">
+        <v>46242</v>
+      </c>
       <c r="C7" s="35"/>
       <c r="D7" s="7" t="s">
         <v>54</v>
@@ -2668,41 +2670,41 @@
       <c r="N14" s="18"/>
     </row>
     <row r="15" spans="1:15" s="66" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="126" t="s">
+      <c r="B15" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="125" t="s">
+      <c r="C15" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="125" t="s">
+      <c r="D15" s="97" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="133" t="s">
+      <c r="E15" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="135" t="s">
+      <c r="F15" s="107" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="119" t="s">
+      <c r="G15" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="121" t="s">
+      <c r="H15" s="94" t="s">
         <v>33</v>
       </c>
       <c r="J15" s="67"/>
     </row>
     <row r="16" spans="1:15" s="66" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="125"/>
-      <c r="B16" s="127"/>
-      <c r="C16" s="125"/>
-      <c r="D16" s="125"/>
-      <c r="E16" s="134"/>
-      <c r="F16" s="136"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="122"/>
+      <c r="A16" s="97"/>
+      <c r="B16" s="99"/>
+      <c r="C16" s="97"/>
+      <c r="D16" s="97"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="95"/>
       <c r="J16" s="67"/>
     </row>
     <row r="17" spans="1:14" s="19" customFormat="1" ht="21" customHeight="1">
@@ -2733,7 +2735,7 @@
         <f>G17*0.00328/F17</f>
         <v>0</v>
       </c>
-      <c r="K17" s="77" t="s">
+      <c r="K17" s="113" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2751,7 +2753,7 @@
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
       <c r="J18" s="18"/>
-      <c r="K18" s="77"/>
+      <c r="K18" s="113"/>
       <c r="M18" s="18"/>
       <c r="N18" s="18"/>
     </row>
@@ -2779,10 +2781,10 @@
       <c r="A20" s="14">
         <v>4</v>
       </c>
-      <c r="B20" s="128" t="s">
+      <c r="B20" s="100" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="129"/>
+      <c r="C20" s="101"/>
       <c r="D20" s="14" t="s">
         <v>52</v>
       </c>
@@ -2915,44 +2917,44 @@
       <c r="N27" s="18"/>
     </row>
     <row r="28" spans="1:14" s="71" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A28" s="123" t="s">
+      <c r="A28" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="123" t="s">
+      <c r="B28" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="123" t="s">
+      <c r="C28" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="123" t="s">
+      <c r="D28" s="96" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="68"/>
-      <c r="F28" s="124" t="s">
+      <c r="F28" s="114" t="s">
         <v>64</v>
       </c>
-      <c r="G28" s="140" t="s">
+      <c r="G28" s="112" t="s">
         <v>57</v>
       </c>
-      <c r="H28" s="140"/>
-      <c r="I28" s="140"/>
-      <c r="J28" s="142"/>
-      <c r="K28" s="140" t="s">
+      <c r="H28" s="112"/>
+      <c r="I28" s="112"/>
+      <c r="J28" s="116"/>
+      <c r="K28" s="112" t="s">
         <v>58</v>
       </c>
-      <c r="L28" s="140"/>
-      <c r="M28" s="140"/>
-      <c r="N28" s="140" t="s">
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:14" s="71" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A29" s="123"/>
-      <c r="B29" s="123"/>
-      <c r="C29" s="123"/>
-      <c r="D29" s="123"/>
+      <c r="A29" s="96"/>
+      <c r="B29" s="96"/>
+      <c r="C29" s="96"/>
+      <c r="D29" s="96"/>
       <c r="E29" s="68"/>
-      <c r="F29" s="124"/>
+      <c r="F29" s="114"/>
       <c r="G29" s="69" t="s">
         <v>59</v>
       </c>
@@ -2974,23 +2976,23 @@
       <c r="M29" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="N29" s="140"/>
+      <c r="N29" s="112"/>
     </row>
     <row r="30" spans="1:14" s="19" customFormat="1" ht="21" customHeight="1">
-      <c r="A30" s="116">
+      <c r="A30" s="89">
         <v>6.1</v>
       </c>
-      <c r="B30" s="130" t="s">
+      <c r="B30" s="102" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="143" t="s">
+      <c r="C30" s="117" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="146">
+      <c r="D30" s="120">
         <v>1</v>
       </c>
       <c r="E30" s="11"/>
-      <c r="F30" s="137">
+      <c r="F30" s="109">
         <f>M8*D30</f>
         <v>0</v>
       </c>
@@ -2998,7 +3000,7 @@
       <c r="H30" s="43"/>
       <c r="I30" s="43"/>
       <c r="J30" s="44"/>
-      <c r="K30" s="141" t="s">
+      <c r="K30" s="115" t="s">
         <v>49</v>
       </c>
       <c r="L30" s="11"/>
@@ -3006,113 +3008,113 @@
       <c r="N30" s="25"/>
     </row>
     <row r="31" spans="1:14" s="19" customFormat="1" ht="21" customHeight="1">
-      <c r="A31" s="117"/>
-      <c r="B31" s="131"/>
-      <c r="C31" s="144"/>
-      <c r="D31" s="147"/>
+      <c r="A31" s="90"/>
+      <c r="B31" s="103"/>
+      <c r="C31" s="118"/>
+      <c r="D31" s="121"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="138"/>
+      <c r="F31" s="110"/>
       <c r="G31" s="43"/>
       <c r="H31" s="43"/>
       <c r="I31" s="43"/>
       <c r="J31" s="44"/>
-      <c r="K31" s="141"/>
+      <c r="K31" s="115"/>
       <c r="L31" s="14"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
     </row>
     <row r="32" spans="1:14" s="19" customFormat="1" ht="21" customHeight="1">
-      <c r="A32" s="117"/>
-      <c r="B32" s="131"/>
-      <c r="C32" s="144"/>
-      <c r="D32" s="147"/>
+      <c r="A32" s="90"/>
+      <c r="B32" s="103"/>
+      <c r="C32" s="118"/>
+      <c r="D32" s="121"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="138"/>
+      <c r="F32" s="110"/>
       <c r="G32" s="43"/>
       <c r="H32" s="43"/>
       <c r="I32" s="43"/>
       <c r="J32" s="44"/>
-      <c r="K32" s="141"/>
+      <c r="K32" s="115"/>
       <c r="L32" s="25"/>
       <c r="M32" s="25"/>
       <c r="N32" s="25"/>
     </row>
     <row r="33" spans="1:14" s="19" customFormat="1" ht="21" customHeight="1">
-      <c r="A33" s="117"/>
-      <c r="B33" s="131"/>
-      <c r="C33" s="144"/>
-      <c r="D33" s="147"/>
+      <c r="A33" s="90"/>
+      <c r="B33" s="103"/>
+      <c r="C33" s="118"/>
+      <c r="D33" s="121"/>
       <c r="E33" s="11"/>
-      <c r="F33" s="138"/>
+      <c r="F33" s="110"/>
       <c r="G33" s="43"/>
       <c r="H33" s="43"/>
       <c r="I33" s="43"/>
       <c r="J33" s="44"/>
-      <c r="K33" s="141"/>
+      <c r="K33" s="115"/>
       <c r="L33" s="25"/>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
     </row>
     <row r="34" spans="1:14" s="19" customFormat="1" ht="21" customHeight="1">
-      <c r="A34" s="117"/>
-      <c r="B34" s="131"/>
-      <c r="C34" s="144"/>
-      <c r="D34" s="147"/>
+      <c r="A34" s="90"/>
+      <c r="B34" s="103"/>
+      <c r="C34" s="118"/>
+      <c r="D34" s="121"/>
       <c r="E34" s="11"/>
-      <c r="F34" s="138"/>
+      <c r="F34" s="110"/>
       <c r="G34" s="43"/>
       <c r="H34" s="43"/>
       <c r="I34" s="43"/>
       <c r="J34" s="44"/>
-      <c r="K34" s="141"/>
+      <c r="K34" s="115"/>
       <c r="L34" s="25"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
     </row>
     <row r="35" spans="1:14" s="19" customFormat="1" ht="21" customHeight="1">
-      <c r="A35" s="117"/>
-      <c r="B35" s="131"/>
-      <c r="C35" s="144"/>
-      <c r="D35" s="147"/>
+      <c r="A35" s="90"/>
+      <c r="B35" s="103"/>
+      <c r="C35" s="118"/>
+      <c r="D35" s="121"/>
       <c r="E35" s="25"/>
-      <c r="F35" s="138"/>
+      <c r="F35" s="110"/>
       <c r="G35" s="43"/>
       <c r="H35" s="43"/>
       <c r="I35" s="43"/>
       <c r="J35" s="44"/>
-      <c r="K35" s="141"/>
+      <c r="K35" s="115"/>
       <c r="L35" s="25"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
     <row r="36" spans="1:14" s="19" customFormat="1" ht="21" customHeight="1">
-      <c r="A36" s="117"/>
-      <c r="B36" s="131"/>
-      <c r="C36" s="144"/>
-      <c r="D36" s="147"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="103"/>
+      <c r="C36" s="118"/>
+      <c r="D36" s="121"/>
       <c r="E36" s="14"/>
-      <c r="F36" s="138"/>
+      <c r="F36" s="110"/>
       <c r="G36" s="43"/>
       <c r="H36" s="43"/>
       <c r="I36" s="43"/>
       <c r="J36" s="44"/>
-      <c r="K36" s="141"/>
+      <c r="K36" s="115"/>
       <c r="L36" s="25"/>
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
     <row r="37" spans="1:14" s="19" customFormat="1" ht="21" customHeight="1">
-      <c r="A37" s="118"/>
-      <c r="B37" s="132"/>
-      <c r="C37" s="145"/>
-      <c r="D37" s="148"/>
+      <c r="A37" s="91"/>
+      <c r="B37" s="104"/>
+      <c r="C37" s="119"/>
+      <c r="D37" s="122"/>
       <c r="E37" s="14"/>
-      <c r="F37" s="139"/>
+      <c r="F37" s="111"/>
       <c r="G37" s="43"/>
       <c r="H37" s="43"/>
       <c r="I37" s="43"/>
       <c r="J37" s="44"/>
-      <c r="K37" s="141"/>
+      <c r="K37" s="115"/>
       <c r="L37" s="25"/>
       <c r="M37" s="25"/>
       <c r="N37" s="25"/>
@@ -3149,69 +3151,69 @@
       <c r="N40" s="18"/>
     </row>
     <row r="41" spans="1:14" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A41" s="85" t="s">
+      <c r="A41" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="B41" s="85" t="s">
+      <c r="B41" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="85" t="s">
+      <c r="C41" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="108" t="s">
+      <c r="D41" s="81" t="s">
         <v>19</v>
       </c>
       <c r="E41" s="29"/>
-      <c r="F41" s="85" t="s">
+      <c r="F41" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="G41" s="85" t="s">
+      <c r="G41" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="H41" s="111" t="s">
+      <c r="H41" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="I41" s="111" t="s">
+      <c r="I41" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="J41" s="111" t="s">
+      <c r="J41" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="K41" s="108" t="s">
+      <c r="K41" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="L41" s="114"/>
-      <c r="M41" s="105" t="s">
+      <c r="L41" s="87"/>
+      <c r="M41" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="N41" s="105"/>
+      <c r="N41" s="77"/>
     </row>
     <row r="42" spans="1:14" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A42" s="106"/>
-      <c r="B42" s="106"/>
-      <c r="C42" s="106"/>
-      <c r="D42" s="109"/>
-      <c r="F42" s="106"/>
-      <c r="G42" s="106"/>
-      <c r="H42" s="112"/>
-      <c r="I42" s="112"/>
-      <c r="J42" s="112"/>
-      <c r="K42" s="110"/>
-      <c r="L42" s="115"/>
-      <c r="M42" s="105"/>
-      <c r="N42" s="105"/>
+      <c r="A42" s="79"/>
+      <c r="B42" s="79"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="82"/>
+      <c r="F42" s="79"/>
+      <c r="G42" s="79"/>
+      <c r="H42" s="85"/>
+      <c r="I42" s="85"/>
+      <c r="J42" s="85"/>
+      <c r="K42" s="83"/>
+      <c r="L42" s="88"/>
+      <c r="M42" s="77"/>
+      <c r="N42" s="77"/>
     </row>
     <row r="43" spans="1:14" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A43" s="107"/>
-      <c r="B43" s="107"/>
-      <c r="C43" s="107"/>
-      <c r="D43" s="110"/>
+      <c r="A43" s="80"/>
+      <c r="B43" s="80"/>
+      <c r="C43" s="80"/>
+      <c r="D43" s="83"/>
       <c r="E43" s="30"/>
-      <c r="F43" s="107"/>
-      <c r="G43" s="107"/>
-      <c r="H43" s="113"/>
-      <c r="I43" s="113"/>
-      <c r="J43" s="113"/>
+      <c r="F43" s="80"/>
+      <c r="G43" s="80"/>
+      <c r="H43" s="86"/>
+      <c r="I43" s="86"/>
+      <c r="J43" s="86"/>
       <c r="K43" s="31" t="s">
         <v>23</v>
       </c>
@@ -3493,205 +3495,205 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13EF0EF5-C5B0-4E3D-8752-BD2726429AB5}">
   <dimension ref="A1:Z83"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.6640625" style="64" customWidth="1"/>
     <col min="2" max="2" width="54" customWidth="1"/>
-    <col min="3" max="20" width="3.19921875" customWidth="1"/>
-    <col min="21" max="26" width="5.46484375" customWidth="1"/>
-    <col min="28" max="28" width="15.3984375" customWidth="1"/>
+    <col min="3" max="20" width="3.21875" customWidth="1"/>
+    <col min="21" max="26" width="5.44140625" customWidth="1"/>
+    <col min="28" max="28" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="80"/>
-      <c r="R1" s="80"/>
-      <c r="S1" s="80"/>
-      <c r="T1" s="80"/>
-      <c r="U1" s="80"/>
-      <c r="V1" s="80"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
+      <c r="N1" s="123"/>
+      <c r="O1" s="123"/>
+      <c r="P1" s="123"/>
+      <c r="Q1" s="123"/>
+      <c r="R1" s="123"/>
+      <c r="S1" s="123"/>
+      <c r="T1" s="123"/>
+      <c r="U1" s="123"/>
+      <c r="V1" s="123"/>
       <c r="W1" s="51"/>
       <c r="X1" s="51"/>
       <c r="Y1" s="51"/>
       <c r="Z1" s="51"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="80"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="80"/>
-      <c r="V2" s="80"/>
+      <c r="A2" s="123"/>
+      <c r="B2" s="123"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="123"/>
+      <c r="P2" s="123"/>
+      <c r="Q2" s="123"/>
+      <c r="R2" s="123"/>
+      <c r="S2" s="123"/>
+      <c r="T2" s="123"/>
+      <c r="U2" s="123"/>
+      <c r="V2" s="123"/>
       <c r="W2" s="51"/>
       <c r="X2" s="51"/>
       <c r="Y2" s="51"/>
       <c r="Z2" s="51"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="80"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="80"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="80"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="80"/>
-      <c r="V3" s="80"/>
+      <c r="A3" s="123"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
+      <c r="M3" s="123"/>
+      <c r="N3" s="123"/>
+      <c r="O3" s="123"/>
+      <c r="P3" s="123"/>
+      <c r="Q3" s="123"/>
+      <c r="R3" s="123"/>
+      <c r="S3" s="123"/>
+      <c r="T3" s="123"/>
+      <c r="U3" s="123"/>
+      <c r="V3" s="123"/>
       <c r="W3" s="51"/>
       <c r="X3" s="51"/>
       <c r="Y3" s="51"/>
       <c r="Z3" s="51"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="80"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
-      <c r="M4" s="80"/>
-      <c r="N4" s="80"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="80"/>
-      <c r="R4" s="80"/>
-      <c r="S4" s="80"/>
-      <c r="T4" s="80"/>
-      <c r="U4" s="80"/>
-      <c r="V4" s="80"/>
+      <c r="A4" s="123"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="123"/>
+      <c r="M4" s="123"/>
+      <c r="N4" s="123"/>
+      <c r="O4" s="123"/>
+      <c r="P4" s="123"/>
+      <c r="Q4" s="123"/>
+      <c r="R4" s="123"/>
+      <c r="S4" s="123"/>
+      <c r="T4" s="123"/>
+      <c r="U4" s="123"/>
+      <c r="V4" s="123"/>
       <c r="W4" s="51"/>
       <c r="X4" s="51"/>
       <c r="Y4" s="51"/>
       <c r="Z4" s="51"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="80"/>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80"/>
-      <c r="P5" s="80"/>
-      <c r="Q5" s="80"/>
-      <c r="R5" s="80"/>
-      <c r="S5" s="80"/>
-      <c r="T5" s="80"/>
-      <c r="U5" s="80"/>
-      <c r="V5" s="80"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="123"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="123"/>
+      <c r="M5" s="123"/>
+      <c r="N5" s="123"/>
+      <c r="O5" s="123"/>
+      <c r="P5" s="123"/>
+      <c r="Q5" s="123"/>
+      <c r="R5" s="123"/>
+      <c r="S5" s="123"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="123"/>
       <c r="W5" s="51"/>
       <c r="X5" s="51"/>
       <c r="Y5" s="51"/>
       <c r="Z5" s="51"/>
     </row>
-    <row r="6" spans="1:26" ht="29.65">
-      <c r="A6" s="81" t="s">
+    <row r="6" spans="1:26" ht="30">
+      <c r="A6" s="124" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
-      <c r="N6" s="81"/>
-      <c r="O6" s="81"/>
-      <c r="P6" s="81"/>
-      <c r="Q6" s="81"/>
-      <c r="R6" s="81"/>
-      <c r="S6" s="81"/>
-      <c r="T6" s="81"/>
-      <c r="U6" s="81"/>
-      <c r="V6" s="81"/>
-      <c r="W6" s="81"/>
-      <c r="X6" s="81"/>
-      <c r="Y6" s="81"/>
-      <c r="Z6" s="81"/>
+      <c r="B6" s="124"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="124"/>
+      <c r="E6" s="124"/>
+      <c r="F6" s="124"/>
+      <c r="G6" s="124"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="124"/>
+      <c r="J6" s="124"/>
+      <c r="K6" s="124"/>
+      <c r="L6" s="124"/>
+      <c r="M6" s="124"/>
+      <c r="N6" s="124"/>
+      <c r="O6" s="124"/>
+      <c r="P6" s="124"/>
+      <c r="Q6" s="124"/>
+      <c r="R6" s="124"/>
+      <c r="S6" s="124"/>
+      <c r="T6" s="124"/>
+      <c r="U6" s="124"/>
+      <c r="V6" s="124"/>
+      <c r="W6" s="124"/>
+      <c r="X6" s="124"/>
+      <c r="Y6" s="124"/>
+      <c r="Z6" s="124"/>
     </row>
     <row r="7" spans="1:26" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A7" s="82" t="s">
+      <c r="A7" s="125" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="82"/>
+      <c r="B7" s="125"/>
       <c r="C7" s="42" t="s">
         <v>74</v>
       </c>
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="78" t="str">
-        <f>'ใบงาน Agilent_JOBB6'!F7</f>
+      <c r="G7" s="126" t="str">
+        <f>'ใบงาน Agilent_JOB 6'!F7</f>
         <v>xxxx</v>
       </c>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
-      <c r="J7" s="78"/>
-      <c r="K7" s="78"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="126"/>
+      <c r="K7" s="126"/>
       <c r="L7" s="18"/>
       <c r="M7" s="18"/>
       <c r="N7" s="18"/>
@@ -3702,20 +3704,20 @@
       <c r="S7" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="W7" s="193" t="str">
-        <f>'ใบงาน Agilent_JOBB6'!M7</f>
+      <c r="W7" s="129" t="str">
+        <f>'ใบงาน Agilent_JOB 6'!M7</f>
         <v>xxxx</v>
       </c>
-      <c r="X7" s="193"/>
-      <c r="Y7" s="193"/>
-      <c r="Z7" s="193"/>
-    </row>
-    <row r="8" spans="1:26" s="6" customFormat="1" ht="13.5">
+      <c r="X7" s="129"/>
+      <c r="Y7" s="129"/>
+      <c r="Z7" s="129"/>
+    </row>
+    <row r="8" spans="1:26" s="6" customFormat="1" ht="13.8">
       <c r="A8" s="7" t="s">
         <v>75</v>
       </c>
       <c r="B8" s="53" t="str">
-        <f>'ใบงาน Agilent_JOBB6'!F8</f>
+        <f>'ใบงาน Agilent_JOB 6'!F8</f>
         <v>K9801-60097</v>
       </c>
       <c r="C8" s="41" t="s">
@@ -3724,13 +3726,13 @@
       <c r="D8" s="41"/>
       <c r="E8" s="41"/>
       <c r="F8" s="41"/>
-      <c r="G8" s="76" t="str">
-        <f>'ใบงาน Agilent_JOBB6'!F9</f>
+      <c r="G8" s="127" t="str">
+        <f>'ใบงาน Agilent_JOB 6'!F9</f>
         <v>-</v>
       </c>
-      <c r="H8" s="76"/>
-      <c r="I8" s="76"/>
-      <c r="J8" s="76"/>
+      <c r="H8" s="127"/>
+      <c r="I8" s="127"/>
+      <c r="J8" s="127"/>
       <c r="K8" s="41"/>
       <c r="L8" s="41"/>
       <c r="M8" s="41"/>
@@ -3743,16 +3745,16 @@
       <c r="T8" s="41"/>
     </row>
     <row r="9" spans="1:26" s="6" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A9" s="82" t="s">
+      <c r="A9" s="125" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="82"/>
-      <c r="G9" s="76" t="s">
+      <c r="B9" s="125"/>
+      <c r="G9" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="H9" s="76"/>
-      <c r="I9" s="76"/>
-      <c r="J9" s="76"/>
+      <c r="H9" s="127"/>
+      <c r="I9" s="127"/>
+      <c r="J9" s="127"/>
       <c r="L9" s="18"/>
       <c r="M9" s="18"/>
       <c r="N9" s="18"/>
@@ -3760,33 +3762,33 @@
       <c r="P9" s="18"/>
       <c r="Q9" s="18"/>
       <c r="R9" s="18"/>
-      <c r="S9" s="77" t="s">
+      <c r="S9" s="113" t="s">
         <v>77</v>
       </c>
-      <c r="T9" s="77"/>
-      <c r="U9" s="77"/>
-      <c r="V9" s="77"/>
+      <c r="T9" s="113"/>
+      <c r="U9" s="113"/>
+      <c r="V9" s="113"/>
     </row>
     <row r="10" spans="1:26" s="6" customFormat="1" ht="13.5" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>78</v>
       </c>
       <c r="B10" s="74">
-        <f>'ใบงาน Agilent_JOBB6'!N8</f>
+        <f>'ใบงาน Agilent_JOB 6'!N8</f>
         <v>2000</v>
       </c>
       <c r="C10" s="18"/>
-      <c r="D10" s="78" t="s">
+      <c r="D10" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="79" t="s">
+      <c r="E10" s="126"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
       <c r="K10" s="42"/>
       <c r="L10" s="18"/>
       <c r="M10" s="18"/>
@@ -3795,24 +3797,24 @@
       <c r="P10" s="18"/>
       <c r="Q10" s="18"/>
       <c r="R10" s="18"/>
-      <c r="S10" s="77"/>
-      <c r="T10" s="77"/>
-      <c r="U10" s="77"/>
-      <c r="V10" s="77"/>
-    </row>
-    <row r="11" spans="1:26" s="6" customFormat="1" ht="13.5">
+      <c r="S10" s="113"/>
+      <c r="T10" s="113"/>
+      <c r="U10" s="113"/>
+      <c r="V10" s="113"/>
+    </row>
+    <row r="11" spans="1:26" s="6" customFormat="1" ht="13.8">
       <c r="A11" s="18"/>
       <c r="B11" s="19"/>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
-      <c r="G11" s="79" t="s">
+      <c r="G11" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
       <c r="K11" s="18"/>
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
@@ -3824,7 +3826,7 @@
       <c r="S11" s="18"/>
       <c r="T11" s="18"/>
     </row>
-    <row r="12" spans="1:26" s="6" customFormat="1" ht="13.5">
+    <row r="12" spans="1:26" s="6" customFormat="1" ht="13.8">
       <c r="A12" s="18" t="s">
         <v>79</v>
       </c>
@@ -3833,12 +3835,12 @@
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="79" t="s">
+      <c r="G12" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
+      <c r="H12" s="128"/>
+      <c r="I12" s="128"/>
+      <c r="J12" s="128"/>
       <c r="K12" s="18"/>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
@@ -3850,7 +3852,7 @@
       <c r="S12" s="18"/>
       <c r="T12" s="18"/>
     </row>
-    <row r="13" spans="1:26" s="6" customFormat="1" ht="13.5">
+    <row r="13" spans="1:26" s="6" customFormat="1" ht="13.8">
       <c r="A13" s="18"/>
       <c r="B13" s="19"/>
       <c r="C13" s="18"/>
@@ -3872,259 +3874,259 @@
       <c r="S13" s="18"/>
       <c r="T13" s="18"/>
     </row>
-    <row r="14" spans="1:26" s="6" customFormat="1" ht="13.5">
-      <c r="A14" s="84" t="s">
+    <row r="14" spans="1:26" s="6" customFormat="1" ht="13.8">
+      <c r="A14" s="138" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="84" t="s">
+      <c r="B14" s="138" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="86" t="s">
+      <c r="C14" s="130" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="87"/>
-      <c r="G14" s="87"/>
-      <c r="H14" s="88"/>
-      <c r="I14" s="86" t="s">
+      <c r="D14" s="139"/>
+      <c r="E14" s="139"/>
+      <c r="F14" s="139"/>
+      <c r="G14" s="139"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="J14" s="87"/>
-      <c r="K14" s="87"/>
-      <c r="L14" s="87"/>
-      <c r="M14" s="87"/>
-      <c r="N14" s="88"/>
-      <c r="O14" s="86" t="s">
+      <c r="J14" s="139"/>
+      <c r="K14" s="139"/>
+      <c r="L14" s="139"/>
+      <c r="M14" s="139"/>
+      <c r="N14" s="140"/>
+      <c r="O14" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-      <c r="R14" s="96"/>
-      <c r="S14" s="96"/>
-      <c r="T14" s="97"/>
-      <c r="U14" s="101" t="s">
+      <c r="P14" s="131"/>
+      <c r="Q14" s="131"/>
+      <c r="R14" s="131"/>
+      <c r="S14" s="131"/>
+      <c r="T14" s="132"/>
+      <c r="U14" s="136" t="s">
         <v>82</v>
       </c>
-      <c r="V14" s="101"/>
-      <c r="W14" s="101"/>
-      <c r="X14" s="101"/>
-      <c r="Y14" s="101"/>
-      <c r="Z14" s="101"/>
-    </row>
-    <row r="15" spans="1:26" s="6" customFormat="1" ht="13.5">
-      <c r="A15" s="85"/>
-      <c r="B15" s="84"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="90"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="90"/>
-      <c r="K15" s="90"/>
-      <c r="L15" s="90"/>
-      <c r="M15" s="90"/>
-      <c r="N15" s="91"/>
-      <c r="O15" s="98"/>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="99"/>
-      <c r="R15" s="99"/>
-      <c r="S15" s="99"/>
-      <c r="T15" s="100"/>
-      <c r="U15" s="101"/>
-      <c r="V15" s="101"/>
-      <c r="W15" s="101"/>
-      <c r="X15" s="101"/>
-      <c r="Y15" s="101"/>
-      <c r="Z15" s="101"/>
-    </row>
-    <row r="16" spans="1:26" s="56" customFormat="1" ht="35.65" customHeight="1">
+      <c r="V14" s="136"/>
+      <c r="W14" s="136"/>
+      <c r="X14" s="136"/>
+      <c r="Y14" s="136"/>
+      <c r="Z14" s="136"/>
+    </row>
+    <row r="15" spans="1:26" s="6" customFormat="1" ht="13.8">
+      <c r="A15" s="78"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="142"/>
+      <c r="E15" s="142"/>
+      <c r="F15" s="142"/>
+      <c r="G15" s="142"/>
+      <c r="H15" s="143"/>
+      <c r="I15" s="141"/>
+      <c r="J15" s="142"/>
+      <c r="K15" s="142"/>
+      <c r="L15" s="142"/>
+      <c r="M15" s="142"/>
+      <c r="N15" s="143"/>
+      <c r="O15" s="133"/>
+      <c r="P15" s="134"/>
+      <c r="Q15" s="134"/>
+      <c r="R15" s="134"/>
+      <c r="S15" s="134"/>
+      <c r="T15" s="135"/>
+      <c r="U15" s="136"/>
+      <c r="V15" s="136"/>
+      <c r="W15" s="136"/>
+      <c r="X15" s="136"/>
+      <c r="Y15" s="136"/>
+      <c r="Z15" s="136"/>
+    </row>
+    <row r="16" spans="1:26" s="56" customFormat="1" ht="35.700000000000003" customHeight="1">
       <c r="A16" s="54">
         <v>1</v>
       </c>
       <c r="B16" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95" t="s">
+      <c r="C16" s="137"/>
+      <c r="D16" s="137"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="137"/>
+      <c r="G16" s="137"/>
+      <c r="H16" s="137"/>
+      <c r="I16" s="137" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="95"/>
-      <c r="K16" s="95"/>
-      <c r="L16" s="95"/>
-      <c r="M16" s="95"/>
-      <c r="N16" s="95"/>
-      <c r="O16" s="95"/>
-      <c r="P16" s="95"/>
-      <c r="Q16" s="95"/>
-      <c r="R16" s="95"/>
-      <c r="S16" s="95"/>
-      <c r="T16" s="95"/>
-      <c r="U16" s="95"/>
-      <c r="V16" s="95"/>
-      <c r="W16" s="95"/>
-      <c r="X16" s="95"/>
-      <c r="Y16" s="95"/>
-      <c r="Z16" s="95"/>
+      <c r="J16" s="137"/>
+      <c r="K16" s="137"/>
+      <c r="L16" s="137"/>
+      <c r="M16" s="137"/>
+      <c r="N16" s="137"/>
+      <c r="O16" s="137"/>
+      <c r="P16" s="137"/>
+      <c r="Q16" s="137"/>
+      <c r="R16" s="137"/>
+      <c r="S16" s="137"/>
+      <c r="T16" s="137"/>
+      <c r="U16" s="137"/>
+      <c r="V16" s="137"/>
+      <c r="W16" s="137"/>
+      <c r="X16" s="137"/>
+      <c r="Y16" s="137"/>
+      <c r="Z16" s="137"/>
     </row>
     <row r="17" spans="1:26" s="56" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="92">
+      <c r="A17" s="144">
         <v>2</v>
       </c>
       <c r="B17" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="95"/>
-      <c r="K17" s="95"/>
-      <c r="L17" s="95"/>
-      <c r="M17" s="95"/>
-      <c r="N17" s="95"/>
-      <c r="O17" s="95"/>
-      <c r="P17" s="95"/>
-      <c r="Q17" s="95"/>
-      <c r="R17" s="95"/>
-      <c r="S17" s="95"/>
-      <c r="T17" s="95"/>
-      <c r="U17" s="95"/>
-      <c r="V17" s="95"/>
-      <c r="W17" s="95"/>
-      <c r="X17" s="95"/>
-      <c r="Y17" s="95"/>
-      <c r="Z17" s="95"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
+      <c r="H17" s="137"/>
+      <c r="I17" s="137"/>
+      <c r="J17" s="137"/>
+      <c r="K17" s="137"/>
+      <c r="L17" s="137"/>
+      <c r="M17" s="137"/>
+      <c r="N17" s="137"/>
+      <c r="O17" s="137"/>
+      <c r="P17" s="137"/>
+      <c r="Q17" s="137"/>
+      <c r="R17" s="137"/>
+      <c r="S17" s="137"/>
+      <c r="T17" s="137"/>
+      <c r="U17" s="137"/>
+      <c r="V17" s="137"/>
+      <c r="W17" s="137"/>
+      <c r="X17" s="137"/>
+      <c r="Y17" s="137"/>
+      <c r="Z17" s="137"/>
     </row>
     <row r="18" spans="1:26" s="56" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A18" s="93"/>
+      <c r="A18" s="145"/>
       <c r="B18" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="95"/>
-      <c r="K18" s="95"/>
-      <c r="L18" s="95"/>
-      <c r="M18" s="95"/>
-      <c r="N18" s="95"/>
-      <c r="O18" s="95"/>
-      <c r="P18" s="95"/>
-      <c r="Q18" s="95"/>
-      <c r="R18" s="95"/>
-      <c r="S18" s="95"/>
-      <c r="T18" s="95"/>
-      <c r="U18" s="95"/>
-      <c r="V18" s="95"/>
-      <c r="W18" s="95"/>
-      <c r="X18" s="95"/>
-      <c r="Y18" s="95"/>
-      <c r="Z18" s="95"/>
+      <c r="C18" s="137"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="137"/>
+      <c r="G18" s="137"/>
+      <c r="H18" s="137"/>
+      <c r="I18" s="137"/>
+      <c r="J18" s="137"/>
+      <c r="K18" s="137"/>
+      <c r="L18" s="137"/>
+      <c r="M18" s="137"/>
+      <c r="N18" s="137"/>
+      <c r="O18" s="137"/>
+      <c r="P18" s="137"/>
+      <c r="Q18" s="137"/>
+      <c r="R18" s="137"/>
+      <c r="S18" s="137"/>
+      <c r="T18" s="137"/>
+      <c r="U18" s="137"/>
+      <c r="V18" s="137"/>
+      <c r="W18" s="137"/>
+      <c r="X18" s="137"/>
+      <c r="Y18" s="137"/>
+      <c r="Z18" s="137"/>
     </row>
     <row r="19" spans="1:26" s="56" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A19" s="93"/>
+      <c r="A19" s="145"/>
       <c r="B19" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="95"/>
-      <c r="K19" s="95"/>
-      <c r="L19" s="95"/>
-      <c r="M19" s="95"/>
-      <c r="N19" s="95"/>
-      <c r="O19" s="95"/>
-      <c r="P19" s="95"/>
-      <c r="Q19" s="95"/>
-      <c r="R19" s="95"/>
-      <c r="S19" s="95"/>
-      <c r="T19" s="95"/>
-      <c r="U19" s="95"/>
-      <c r="V19" s="95"/>
-      <c r="W19" s="95"/>
-      <c r="X19" s="95"/>
-      <c r="Y19" s="95"/>
-      <c r="Z19" s="95"/>
+      <c r="C19" s="137"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="137"/>
+      <c r="G19" s="137"/>
+      <c r="H19" s="137"/>
+      <c r="I19" s="137"/>
+      <c r="J19" s="137"/>
+      <c r="K19" s="137"/>
+      <c r="L19" s="137"/>
+      <c r="M19" s="137"/>
+      <c r="N19" s="137"/>
+      <c r="O19" s="137"/>
+      <c r="P19" s="137"/>
+      <c r="Q19" s="137"/>
+      <c r="R19" s="137"/>
+      <c r="S19" s="137"/>
+      <c r="T19" s="137"/>
+      <c r="U19" s="137"/>
+      <c r="V19" s="137"/>
+      <c r="W19" s="137"/>
+      <c r="X19" s="137"/>
+      <c r="Y19" s="137"/>
+      <c r="Z19" s="137"/>
     </row>
     <row r="20" spans="1:26" s="56" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A20" s="93"/>
+      <c r="A20" s="145"/>
       <c r="B20" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="95"/>
-      <c r="D20" s="95"/>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="95"/>
-      <c r="I20" s="95"/>
-      <c r="J20" s="95"/>
-      <c r="K20" s="95"/>
-      <c r="L20" s="95"/>
-      <c r="M20" s="95"/>
-      <c r="N20" s="95"/>
-      <c r="O20" s="95"/>
-      <c r="P20" s="95"/>
-      <c r="Q20" s="95"/>
-      <c r="R20" s="95"/>
-      <c r="S20" s="95"/>
-      <c r="T20" s="95"/>
-      <c r="U20" s="95"/>
-      <c r="V20" s="95"/>
-      <c r="W20" s="95"/>
-      <c r="X20" s="95"/>
-      <c r="Y20" s="95"/>
-      <c r="Z20" s="95"/>
+      <c r="C20" s="137"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="137"/>
+      <c r="G20" s="137"/>
+      <c r="H20" s="137"/>
+      <c r="I20" s="137"/>
+      <c r="J20" s="137"/>
+      <c r="K20" s="137"/>
+      <c r="L20" s="137"/>
+      <c r="M20" s="137"/>
+      <c r="N20" s="137"/>
+      <c r="O20" s="137"/>
+      <c r="P20" s="137"/>
+      <c r="Q20" s="137"/>
+      <c r="R20" s="137"/>
+      <c r="S20" s="137"/>
+      <c r="T20" s="137"/>
+      <c r="U20" s="137"/>
+      <c r="V20" s="137"/>
+      <c r="W20" s="137"/>
+      <c r="X20" s="137"/>
+      <c r="Y20" s="137"/>
+      <c r="Z20" s="137"/>
     </row>
     <row r="21" spans="1:26" s="56" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A21" s="94"/>
+      <c r="A21" s="146"/>
       <c r="B21" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="95"/>
-      <c r="D21" s="95"/>
-      <c r="E21" s="95"/>
-      <c r="F21" s="95"/>
-      <c r="G21" s="95"/>
-      <c r="H21" s="95"/>
-      <c r="I21" s="95"/>
-      <c r="J21" s="95"/>
-      <c r="K21" s="95"/>
-      <c r="L21" s="95"/>
-      <c r="M21" s="95"/>
-      <c r="N21" s="95"/>
-      <c r="O21" s="95"/>
-      <c r="P21" s="95"/>
-      <c r="Q21" s="95"/>
-      <c r="R21" s="95"/>
-      <c r="S21" s="95"/>
-      <c r="T21" s="95"/>
-      <c r="U21" s="95"/>
-      <c r="V21" s="95"/>
-      <c r="W21" s="95"/>
-      <c r="X21" s="95"/>
-      <c r="Y21" s="95"/>
-      <c r="Z21" s="95"/>
+      <c r="C21" s="137"/>
+      <c r="D21" s="137"/>
+      <c r="E21" s="137"/>
+      <c r="F21" s="137"/>
+      <c r="G21" s="137"/>
+      <c r="H21" s="137"/>
+      <c r="I21" s="137"/>
+      <c r="J21" s="137"/>
+      <c r="K21" s="137"/>
+      <c r="L21" s="137"/>
+      <c r="M21" s="137"/>
+      <c r="N21" s="137"/>
+      <c r="O21" s="137"/>
+      <c r="P21" s="137"/>
+      <c r="Q21" s="137"/>
+      <c r="R21" s="137"/>
+      <c r="S21" s="137"/>
+      <c r="T21" s="137"/>
+      <c r="U21" s="137"/>
+      <c r="V21" s="137"/>
+      <c r="W21" s="137"/>
+      <c r="X21" s="137"/>
+      <c r="Y21" s="137"/>
+      <c r="Z21" s="137"/>
     </row>
     <row r="22" spans="1:26" s="56" customFormat="1" ht="22.5" customHeight="1">
       <c r="A22" s="54">
@@ -4133,30 +4135,30 @@
       <c r="B22" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="95"/>
-      <c r="D22" s="95"/>
-      <c r="E22" s="95"/>
-      <c r="F22" s="95"/>
-      <c r="G22" s="95"/>
-      <c r="H22" s="95"/>
-      <c r="I22" s="95"/>
-      <c r="J22" s="95"/>
-      <c r="K22" s="95"/>
-      <c r="L22" s="95"/>
-      <c r="M22" s="95"/>
-      <c r="N22" s="95"/>
-      <c r="O22" s="95"/>
-      <c r="P22" s="95"/>
-      <c r="Q22" s="95"/>
-      <c r="R22" s="95"/>
-      <c r="S22" s="95"/>
-      <c r="T22" s="95"/>
-      <c r="U22" s="95"/>
-      <c r="V22" s="95"/>
-      <c r="W22" s="95"/>
-      <c r="X22" s="95"/>
-      <c r="Y22" s="95"/>
-      <c r="Z22" s="95"/>
+      <c r="C22" s="137"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="137"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="137"/>
+      <c r="I22" s="137"/>
+      <c r="J22" s="137"/>
+      <c r="K22" s="137"/>
+      <c r="L22" s="137"/>
+      <c r="M22" s="137"/>
+      <c r="N22" s="137"/>
+      <c r="O22" s="137"/>
+      <c r="P22" s="137"/>
+      <c r="Q22" s="137"/>
+      <c r="R22" s="137"/>
+      <c r="S22" s="137"/>
+      <c r="T22" s="137"/>
+      <c r="U22" s="137"/>
+      <c r="V22" s="137"/>
+      <c r="W22" s="137"/>
+      <c r="X22" s="137"/>
+      <c r="Y22" s="137"/>
+      <c r="Z22" s="137"/>
     </row>
     <row r="23" spans="1:26" s="56" customFormat="1" ht="22.5" customHeight="1">
       <c r="A23" s="54">
@@ -4165,30 +4167,30 @@
       <c r="B23" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="95"/>
-      <c r="D23" s="95"/>
-      <c r="E23" s="95"/>
-      <c r="F23" s="95"/>
-      <c r="G23" s="95"/>
-      <c r="H23" s="95"/>
-      <c r="I23" s="95"/>
-      <c r="J23" s="95"/>
-      <c r="K23" s="95"/>
-      <c r="L23" s="95"/>
-      <c r="M23" s="95"/>
-      <c r="N23" s="95"/>
-      <c r="O23" s="95"/>
-      <c r="P23" s="95"/>
-      <c r="Q23" s="95"/>
-      <c r="R23" s="95"/>
-      <c r="S23" s="95"/>
-      <c r="T23" s="95"/>
-      <c r="U23" s="95"/>
-      <c r="V23" s="95"/>
-      <c r="W23" s="95"/>
-      <c r="X23" s="95"/>
-      <c r="Y23" s="95"/>
-      <c r="Z23" s="95"/>
+      <c r="C23" s="137"/>
+      <c r="D23" s="137"/>
+      <c r="E23" s="137"/>
+      <c r="F23" s="137"/>
+      <c r="G23" s="137"/>
+      <c r="H23" s="137"/>
+      <c r="I23" s="137"/>
+      <c r="J23" s="137"/>
+      <c r="K23" s="137"/>
+      <c r="L23" s="137"/>
+      <c r="M23" s="137"/>
+      <c r="N23" s="137"/>
+      <c r="O23" s="137"/>
+      <c r="P23" s="137"/>
+      <c r="Q23" s="137"/>
+      <c r="R23" s="137"/>
+      <c r="S23" s="137"/>
+      <c r="T23" s="137"/>
+      <c r="U23" s="137"/>
+      <c r="V23" s="137"/>
+      <c r="W23" s="137"/>
+      <c r="X23" s="137"/>
+      <c r="Y23" s="137"/>
+      <c r="Z23" s="137"/>
     </row>
     <row r="24" spans="1:26" s="56" customFormat="1" ht="22.5" customHeight="1">
       <c r="A24" s="54">
@@ -4197,89 +4199,89 @@
       <c r="B24" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="95"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
-      <c r="F24" s="95"/>
-      <c r="G24" s="95"/>
-      <c r="H24" s="95"/>
-      <c r="I24" s="95"/>
-      <c r="J24" s="95"/>
-      <c r="K24" s="95"/>
-      <c r="L24" s="95"/>
-      <c r="M24" s="95"/>
-      <c r="N24" s="95"/>
-      <c r="O24" s="95"/>
-      <c r="P24" s="95"/>
-      <c r="Q24" s="95"/>
-      <c r="R24" s="95"/>
-      <c r="S24" s="95"/>
-      <c r="T24" s="95"/>
-      <c r="U24" s="95"/>
-      <c r="V24" s="95"/>
-      <c r="W24" s="95"/>
-      <c r="X24" s="95"/>
-      <c r="Y24" s="95"/>
-      <c r="Z24" s="95"/>
-    </row>
-    <row r="25" spans="1:26" s="56" customFormat="1" ht="20.65" customHeight="1">
+      <c r="C24" s="137"/>
+      <c r="D24" s="137"/>
+      <c r="E24" s="137"/>
+      <c r="F24" s="137"/>
+      <c r="G24" s="137"/>
+      <c r="H24" s="137"/>
+      <c r="I24" s="137"/>
+      <c r="J24" s="137"/>
+      <c r="K24" s="137"/>
+      <c r="L24" s="137"/>
+      <c r="M24" s="137"/>
+      <c r="N24" s="137"/>
+      <c r="O24" s="137"/>
+      <c r="P24" s="137"/>
+      <c r="Q24" s="137"/>
+      <c r="R24" s="137"/>
+      <c r="S24" s="137"/>
+      <c r="T24" s="137"/>
+      <c r="U24" s="137"/>
+      <c r="V24" s="137"/>
+      <c r="W24" s="137"/>
+      <c r="X24" s="137"/>
+      <c r="Y24" s="137"/>
+      <c r="Z24" s="137"/>
+    </row>
+    <row r="25" spans="1:26" s="56" customFormat="1" ht="20.7" customHeight="1">
       <c r="A25" s="54">
         <v>6</v>
       </c>
       <c r="B25" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C25" s="95"/>
-      <c r="D25" s="95"/>
-      <c r="E25" s="95"/>
-      <c r="F25" s="95"/>
-      <c r="G25" s="95"/>
-      <c r="H25" s="95"/>
-      <c r="I25" s="95"/>
-      <c r="J25" s="95"/>
-      <c r="K25" s="95"/>
-      <c r="L25" s="95"/>
-      <c r="M25" s="95"/>
-      <c r="N25" s="95"/>
-      <c r="O25" s="95"/>
-      <c r="P25" s="95"/>
-      <c r="Q25" s="95"/>
-      <c r="R25" s="95"/>
-      <c r="S25" s="95"/>
-      <c r="T25" s="95"/>
-      <c r="U25" s="95"/>
-      <c r="V25" s="95"/>
-      <c r="W25" s="95"/>
-      <c r="X25" s="95"/>
-      <c r="Y25" s="95"/>
-      <c r="Z25" s="95"/>
-    </row>
-    <row r="26" spans="1:26" s="6" customFormat="1" ht="13.5">
+      <c r="C25" s="137"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="137"/>
+      <c r="F25" s="137"/>
+      <c r="G25" s="137"/>
+      <c r="H25" s="137"/>
+      <c r="I25" s="137"/>
+      <c r="J25" s="137"/>
+      <c r="K25" s="137"/>
+      <c r="L25" s="137"/>
+      <c r="M25" s="137"/>
+      <c r="N25" s="137"/>
+      <c r="O25" s="137"/>
+      <c r="P25" s="137"/>
+      <c r="Q25" s="137"/>
+      <c r="R25" s="137"/>
+      <c r="S25" s="137"/>
+      <c r="T25" s="137"/>
+      <c r="U25" s="137"/>
+      <c r="V25" s="137"/>
+      <c r="W25" s="137"/>
+      <c r="X25" s="137"/>
+      <c r="Y25" s="137"/>
+      <c r="Z25" s="137"/>
+    </row>
+    <row r="26" spans="1:26" s="6" customFormat="1" ht="13.8">
       <c r="A26" s="7"/>
-      <c r="C26" s="102"/>
-      <c r="D26" s="102"/>
-      <c r="E26" s="102"/>
-      <c r="F26" s="102"/>
-    </row>
-    <row r="27" spans="1:26" s="6" customFormat="1" ht="15">
-      <c r="A27" s="149" t="s">
+      <c r="C26" s="147"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="147"/>
+      <c r="F26" s="147"/>
+    </row>
+    <row r="27" spans="1:26" s="6" customFormat="1" ht="15.6">
+      <c r="A27" s="148" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="149"/>
-      <c r="C27" s="149"/>
-      <c r="D27" s="149"/>
-      <c r="E27" s="149"/>
-      <c r="F27" s="149"/>
-      <c r="G27" s="149"/>
-      <c r="H27" s="149"/>
-      <c r="I27" s="149"/>
-      <c r="J27" s="149"/>
+      <c r="B27" s="148"/>
+      <c r="C27" s="148"/>
+      <c r="D27" s="148"/>
+      <c r="E27" s="148"/>
+      <c r="F27" s="148"/>
+      <c r="G27" s="148"/>
+      <c r="H27" s="148"/>
+      <c r="I27" s="148"/>
+      <c r="J27" s="148"/>
     </row>
     <row r="28" spans="1:26" s="58" customFormat="1" ht="15">
-      <c r="A28" s="150" t="s">
+      <c r="A28" s="149" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="151"/>
+      <c r="B28" s="150"/>
       <c r="C28" s="153" t="s">
         <v>95</v>
       </c>
@@ -4292,76 +4294,76 @@
       <c r="H28" s="155"/>
       <c r="I28" s="155"/>
       <c r="J28" s="156"/>
-      <c r="L28" s="103" t="s">
+      <c r="L28" s="152" t="s">
         <v>3</v>
       </c>
-      <c r="M28" s="103"/>
+      <c r="M28" s="152"/>
     </row>
     <row r="29" spans="1:26" s="58" customFormat="1" ht="15">
-      <c r="A29" s="150" t="s">
+      <c r="A29" s="149" t="s">
         <v>97</v>
       </c>
-      <c r="B29" s="151"/>
-      <c r="C29" s="152">
+      <c r="B29" s="150"/>
+      <c r="C29" s="151">
         <v>10</v>
       </c>
-      <c r="D29" s="152"/>
-      <c r="E29" s="152"/>
-      <c r="F29" s="152"/>
-      <c r="G29" s="152">
+      <c r="D29" s="151"/>
+      <c r="E29" s="151"/>
+      <c r="F29" s="151"/>
+      <c r="G29" s="151">
         <v>10</v>
       </c>
-      <c r="H29" s="152"/>
-      <c r="I29" s="152"/>
-      <c r="J29" s="152"/>
-      <c r="L29" s="103"/>
-      <c r="M29" s="103"/>
+      <c r="H29" s="151"/>
+      <c r="I29" s="151"/>
+      <c r="J29" s="151"/>
+      <c r="L29" s="152"/>
+      <c r="M29" s="152"/>
     </row>
     <row r="30" spans="1:26" s="58" customFormat="1" ht="15">
-      <c r="A30" s="150" t="s">
+      <c r="A30" s="149" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="151"/>
-      <c r="C30" s="152">
+      <c r="B30" s="150"/>
+      <c r="C30" s="151">
         <v>20</v>
       </c>
-      <c r="D30" s="152"/>
-      <c r="E30" s="152"/>
-      <c r="F30" s="152"/>
-      <c r="G30" s="152">
+      <c r="D30" s="151"/>
+      <c r="E30" s="151"/>
+      <c r="F30" s="151"/>
+      <c r="G30" s="151">
         <v>20</v>
       </c>
-      <c r="H30" s="152"/>
-      <c r="I30" s="152"/>
-      <c r="J30" s="152"/>
-      <c r="L30" s="103"/>
-      <c r="M30" s="103"/>
+      <c r="H30" s="151"/>
+      <c r="I30" s="151"/>
+      <c r="J30" s="151"/>
+      <c r="L30" s="152"/>
+      <c r="M30" s="152"/>
     </row>
     <row r="31" spans="1:26" s="58" customFormat="1" ht="15">
-      <c r="A31" s="150" t="s">
+      <c r="A31" s="149" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="151"/>
-      <c r="C31" s="152">
+      <c r="B31" s="150"/>
+      <c r="C31" s="151">
         <v>30</v>
       </c>
-      <c r="D31" s="152"/>
-      <c r="E31" s="152"/>
-      <c r="F31" s="152"/>
-      <c r="G31" s="152">
+      <c r="D31" s="151"/>
+      <c r="E31" s="151"/>
+      <c r="F31" s="151"/>
+      <c r="G31" s="151">
         <v>30</v>
       </c>
-      <c r="H31" s="152"/>
-      <c r="I31" s="152"/>
-      <c r="J31" s="152"/>
-      <c r="L31" s="103"/>
-      <c r="M31" s="103"/>
+      <c r="H31" s="151"/>
+      <c r="I31" s="151"/>
+      <c r="J31" s="151"/>
+      <c r="L31" s="152"/>
+      <c r="M31" s="152"/>
     </row>
     <row r="32" spans="1:26" s="58" customFormat="1" ht="15">
-      <c r="A32" s="150" t="s">
+      <c r="A32" s="149" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="151"/>
+      <c r="B32" s="150"/>
       <c r="C32" s="157">
         <v>40</v>
       </c>
@@ -4374,74 +4376,74 @@
       <c r="H32" s="158"/>
       <c r="I32" s="158"/>
       <c r="J32" s="159"/>
-      <c r="L32" s="103"/>
-      <c r="M32" s="103"/>
+      <c r="L32" s="152"/>
+      <c r="M32" s="152"/>
     </row>
     <row r="33" spans="1:26" s="58" customFormat="1" ht="15">
-      <c r="A33" s="150" t="s">
+      <c r="A33" s="149" t="s">
         <v>101</v>
       </c>
-      <c r="B33" s="151"/>
-      <c r="C33" s="152">
+      <c r="B33" s="150"/>
+      <c r="C33" s="151">
         <v>50</v>
       </c>
-      <c r="D33" s="152"/>
-      <c r="E33" s="152"/>
-      <c r="F33" s="152"/>
-      <c r="G33" s="152">
+      <c r="D33" s="151"/>
+      <c r="E33" s="151"/>
+      <c r="F33" s="151"/>
+      <c r="G33" s="151">
         <v>50</v>
       </c>
-      <c r="H33" s="152"/>
-      <c r="I33" s="152"/>
-      <c r="J33" s="152"/>
-      <c r="L33" s="103"/>
-      <c r="M33" s="103"/>
+      <c r="H33" s="151"/>
+      <c r="I33" s="151"/>
+      <c r="J33" s="151"/>
+      <c r="L33" s="152"/>
+      <c r="M33" s="152"/>
     </row>
     <row r="34" spans="1:26" s="58" customFormat="1" ht="15">
-      <c r="A34" s="150" t="s">
+      <c r="A34" s="149" t="s">
         <v>102</v>
       </c>
-      <c r="B34" s="151"/>
-      <c r="C34" s="152">
+      <c r="B34" s="150"/>
+      <c r="C34" s="151">
         <v>100</v>
       </c>
-      <c r="D34" s="152"/>
-      <c r="E34" s="152"/>
-      <c r="F34" s="152"/>
-      <c r="G34" s="152">
+      <c r="D34" s="151"/>
+      <c r="E34" s="151"/>
+      <c r="F34" s="151"/>
+      <c r="G34" s="151">
         <v>100</v>
       </c>
-      <c r="H34" s="152"/>
-      <c r="I34" s="152"/>
-      <c r="J34" s="152"/>
-      <c r="L34" s="103"/>
-      <c r="M34" s="103"/>
+      <c r="H34" s="151"/>
+      <c r="I34" s="151"/>
+      <c r="J34" s="151"/>
+      <c r="L34" s="152"/>
+      <c r="M34" s="152"/>
     </row>
     <row r="35" spans="1:26" s="58" customFormat="1" ht="15">
-      <c r="A35" s="150" t="s">
+      <c r="A35" s="149" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="151"/>
-      <c r="C35" s="152">
+      <c r="B35" s="150"/>
+      <c r="C35" s="151">
         <v>200</v>
       </c>
-      <c r="D35" s="152"/>
-      <c r="E35" s="152"/>
-      <c r="F35" s="152"/>
-      <c r="G35" s="152">
+      <c r="D35" s="151"/>
+      <c r="E35" s="151"/>
+      <c r="F35" s="151"/>
+      <c r="G35" s="151">
         <v>200</v>
       </c>
-      <c r="H35" s="152"/>
-      <c r="I35" s="152"/>
-      <c r="J35" s="152"/>
-      <c r="L35" s="103"/>
-      <c r="M35" s="103"/>
+      <c r="H35" s="151"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="151"/>
+      <c r="L35" s="152"/>
+      <c r="M35" s="152"/>
     </row>
     <row r="36" spans="1:26" s="58" customFormat="1" ht="15">
-      <c r="A36" s="150" t="s">
+      <c r="A36" s="149" t="s">
         <v>104</v>
       </c>
-      <c r="B36" s="151"/>
+      <c r="B36" s="150"/>
       <c r="C36" s="157" t="s">
         <v>105</v>
       </c>
@@ -4452,35 +4454,35 @@
       <c r="H36" s="158"/>
       <c r="I36" s="158"/>
       <c r="J36" s="159"/>
-      <c r="L36" s="103"/>
-      <c r="M36" s="103"/>
+      <c r="L36" s="152"/>
+      <c r="M36" s="152"/>
     </row>
     <row r="37" spans="1:26" s="58" customFormat="1" ht="15">
       <c r="A37" s="59"/>
-      <c r="L37" s="103"/>
-      <c r="M37" s="103"/>
+      <c r="L37" s="152"/>
+      <c r="M37" s="152"/>
     </row>
     <row r="38" spans="1:26" s="58" customFormat="1" ht="15">
       <c r="A38" s="59"/>
-      <c r="L38" s="103"/>
-      <c r="M38" s="103"/>
-    </row>
-    <row r="39" spans="1:26" s="6" customFormat="1" ht="13.5">
+      <c r="L38" s="152"/>
+      <c r="M38" s="152"/>
+    </row>
+    <row r="39" spans="1:26" s="6" customFormat="1" ht="13.8">
       <c r="A39" s="7"/>
-      <c r="L39" s="102"/>
-      <c r="M39" s="102"/>
-    </row>
-    <row r="40" spans="1:26" s="6" customFormat="1" ht="13.5">
+      <c r="L39" s="147"/>
+      <c r="M39" s="147"/>
+    </row>
+    <row r="40" spans="1:26" s="6" customFormat="1" ht="13.8">
       <c r="A40" s="7"/>
-      <c r="L40" s="102"/>
-      <c r="M40" s="102"/>
-    </row>
-    <row r="41" spans="1:26" s="6" customFormat="1" ht="13.5">
+      <c r="L40" s="147"/>
+      <c r="M40" s="147"/>
+    </row>
+    <row r="41" spans="1:26" s="6" customFormat="1" ht="13.8">
       <c r="A41" s="7"/>
-      <c r="L41" s="102"/>
-      <c r="M41" s="102"/>
-    </row>
-    <row r="42" spans="1:26" s="58" customFormat="1" ht="19.25" customHeight="1">
+      <c r="L41" s="147"/>
+      <c r="M41" s="147"/>
+    </row>
+    <row r="42" spans="1:26" s="58" customFormat="1" ht="19.2" customHeight="1">
       <c r="A42" s="13" t="s">
         <v>106</v>
       </c>
@@ -6054,7 +6056,7 @@
       <c r="Y81" s="167"/>
       <c r="Z81" s="168"/>
     </row>
-    <row r="82" spans="1:26" s="6" customFormat="1" ht="20.350000000000001" customHeight="1">
+    <row r="82" spans="1:26" s="6" customFormat="1" ht="20.399999999999999" customHeight="1">
       <c r="A82" s="7" t="s">
         <v>3</v>
       </c>
@@ -6083,7 +6085,7 @@
       <c r="Y82" s="192"/>
       <c r="Z82" s="192"/>
     </row>
-    <row r="83" spans="1:26" ht="15.75">
+    <row r="83" spans="1:26" ht="15.6">
       <c r="A83" s="62"/>
       <c r="B83" s="63"/>
       <c r="C83" s="63"/>
@@ -6397,204 +6399,204 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z28"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.796875" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" customWidth="1"/>
     <col min="2" max="2" width="56.33203125" customWidth="1"/>
-    <col min="3" max="18" width="3.9296875" customWidth="1"/>
-    <col min="19" max="20" width="4.3984375" customWidth="1"/>
-    <col min="21" max="26" width="4.9296875" customWidth="1"/>
+    <col min="3" max="18" width="3.88671875" customWidth="1"/>
+    <col min="19" max="20" width="4.44140625" customWidth="1"/>
+    <col min="21" max="26" width="4.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="80"/>
-      <c r="R1" s="80"/>
-      <c r="S1" s="80"/>
-      <c r="T1" s="80"/>
-      <c r="U1" s="80"/>
-      <c r="V1" s="80"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
+      <c r="N1" s="123"/>
+      <c r="O1" s="123"/>
+      <c r="P1" s="123"/>
+      <c r="Q1" s="123"/>
+      <c r="R1" s="123"/>
+      <c r="S1" s="123"/>
+      <c r="T1" s="123"/>
+      <c r="U1" s="123"/>
+      <c r="V1" s="123"/>
       <c r="W1" s="51"/>
       <c r="X1" s="51"/>
       <c r="Y1" s="51"/>
       <c r="Z1" s="51"/>
     </row>
     <row r="2" spans="1:26" ht="15">
-      <c r="A2" s="80"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="80"/>
-      <c r="V2" s="80"/>
+      <c r="A2" s="123"/>
+      <c r="B2" s="123"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="123"/>
+      <c r="P2" s="123"/>
+      <c r="Q2" s="123"/>
+      <c r="R2" s="123"/>
+      <c r="S2" s="123"/>
+      <c r="T2" s="123"/>
+      <c r="U2" s="123"/>
+      <c r="V2" s="123"/>
       <c r="W2" s="51"/>
       <c r="X2" s="51"/>
       <c r="Y2" s="51"/>
       <c r="Z2" s="51"/>
     </row>
     <row r="3" spans="1:26" ht="15">
-      <c r="A3" s="80"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="80"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="80"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="80"/>
-      <c r="V3" s="80"/>
+      <c r="A3" s="123"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
+      <c r="M3" s="123"/>
+      <c r="N3" s="123"/>
+      <c r="O3" s="123"/>
+      <c r="P3" s="123"/>
+      <c r="Q3" s="123"/>
+      <c r="R3" s="123"/>
+      <c r="S3" s="123"/>
+      <c r="T3" s="123"/>
+      <c r="U3" s="123"/>
+      <c r="V3" s="123"/>
       <c r="W3" s="51"/>
       <c r="X3" s="51"/>
       <c r="Y3" s="51"/>
       <c r="Z3" s="51"/>
     </row>
     <row r="4" spans="1:26" ht="15">
-      <c r="A4" s="80"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
-      <c r="M4" s="80"/>
-      <c r="N4" s="80"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="80"/>
-      <c r="R4" s="80"/>
-      <c r="S4" s="80"/>
-      <c r="T4" s="80"/>
-      <c r="U4" s="80"/>
-      <c r="V4" s="80"/>
+      <c r="A4" s="123"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="123"/>
+      <c r="M4" s="123"/>
+      <c r="N4" s="123"/>
+      <c r="O4" s="123"/>
+      <c r="P4" s="123"/>
+      <c r="Q4" s="123"/>
+      <c r="R4" s="123"/>
+      <c r="S4" s="123"/>
+      <c r="T4" s="123"/>
+      <c r="U4" s="123"/>
+      <c r="V4" s="123"/>
       <c r="W4" s="51"/>
       <c r="X4" s="51"/>
       <c r="Y4" s="51"/>
       <c r="Z4" s="51"/>
     </row>
     <row r="5" spans="1:26" ht="15">
-      <c r="A5" s="80"/>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80"/>
-      <c r="P5" s="80"/>
-      <c r="Q5" s="80"/>
-      <c r="R5" s="80"/>
-      <c r="S5" s="80"/>
-      <c r="T5" s="80"/>
-      <c r="U5" s="80"/>
-      <c r="V5" s="80"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="123"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="123"/>
+      <c r="M5" s="123"/>
+      <c r="N5" s="123"/>
+      <c r="O5" s="123"/>
+      <c r="P5" s="123"/>
+      <c r="Q5" s="123"/>
+      <c r="R5" s="123"/>
+      <c r="S5" s="123"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="123"/>
       <c r="W5" s="51"/>
       <c r="X5" s="51"/>
       <c r="Y5" s="51"/>
       <c r="Z5" s="51"/>
     </row>
-    <row r="6" spans="1:26" ht="29.65">
-      <c r="A6" s="81" t="s">
+    <row r="6" spans="1:26" ht="30">
+      <c r="A6" s="124" t="s">
         <v>220</v>
       </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
-      <c r="N6" s="81"/>
-      <c r="O6" s="81"/>
-      <c r="P6" s="81"/>
-      <c r="Q6" s="81"/>
-      <c r="R6" s="81"/>
-      <c r="S6" s="81"/>
-      <c r="T6" s="81"/>
-      <c r="U6" s="81"/>
-      <c r="V6" s="81"/>
-      <c r="W6" s="81"/>
-      <c r="X6" s="81"/>
-      <c r="Y6" s="81"/>
-      <c r="Z6" s="81"/>
-    </row>
-    <row r="7" spans="1:26" s="6" customFormat="1" ht="17.25">
-      <c r="A7" s="82" t="s">
+      <c r="B6" s="124"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="124"/>
+      <c r="E6" s="124"/>
+      <c r="F6" s="124"/>
+      <c r="G6" s="124"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="124"/>
+      <c r="J6" s="124"/>
+      <c r="K6" s="124"/>
+      <c r="L6" s="124"/>
+      <c r="M6" s="124"/>
+      <c r="N6" s="124"/>
+      <c r="O6" s="124"/>
+      <c r="P6" s="124"/>
+      <c r="Q6" s="124"/>
+      <c r="R6" s="124"/>
+      <c r="S6" s="124"/>
+      <c r="T6" s="124"/>
+      <c r="U6" s="124"/>
+      <c r="V6" s="124"/>
+      <c r="W6" s="124"/>
+      <c r="X6" s="124"/>
+      <c r="Y6" s="124"/>
+      <c r="Z6" s="124"/>
+    </row>
+    <row r="7" spans="1:26" s="6" customFormat="1" ht="17.399999999999999">
+      <c r="A7" s="125" t="s">
         <v>220</v>
       </c>
-      <c r="B7" s="82"/>
+      <c r="B7" s="125"/>
       <c r="C7" s="42" t="s">
         <v>74</v>
       </c>
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="78" t="str">
-        <f>'ใบงาน Agilent_JOBB6'!F7</f>
+      <c r="G7" s="126" t="str">
+        <f>'ใบงาน Agilent_JOB 6'!F7</f>
         <v>xxxx</v>
       </c>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
-      <c r="J7" s="78"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="126"/>
       <c r="L7" s="18"/>
       <c r="M7" s="18"/>
       <c r="N7" s="18"/>
@@ -6605,20 +6607,20 @@
       <c r="S7" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="W7" s="193" t="str">
-        <f>'ใบงาน Agilent_JOBB6'!M7</f>
+      <c r="W7" s="129" t="str">
+        <f>'ใบงาน Agilent_JOB 6'!M7</f>
         <v>xxxx</v>
       </c>
-      <c r="X7" s="193"/>
-      <c r="Y7" s="193"/>
-      <c r="Z7" s="193"/>
+      <c r="X7" s="129"/>
+      <c r="Y7" s="129"/>
+      <c r="Z7" s="129"/>
     </row>
     <row r="8" spans="1:26" s="6" customFormat="1" ht="24.75" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>75</v>
       </c>
       <c r="B8" s="53" t="str">
-        <f>'ใบงาน Agilent_JOBB6'!F8</f>
+        <f>'ใบงาน Agilent_JOB 6'!F8</f>
         <v>K9801-60097</v>
       </c>
       <c r="C8" s="53" t="s">
@@ -6627,13 +6629,13 @@
       <c r="D8" s="53"/>
       <c r="E8" s="53"/>
       <c r="F8" s="53"/>
-      <c r="G8" s="76" t="str">
-        <f>'ใบงาน Agilent_JOBB6'!F9</f>
+      <c r="G8" s="127" t="str">
+        <f>'ใบงาน Agilent_JOB 6'!F9</f>
         <v>-</v>
       </c>
-      <c r="H8" s="76"/>
-      <c r="I8" s="76"/>
-      <c r="J8" s="76"/>
+      <c r="H8" s="127"/>
+      <c r="I8" s="127"/>
+      <c r="J8" s="127"/>
       <c r="K8" s="41"/>
       <c r="L8" s="41"/>
       <c r="M8" s="41"/>
@@ -6647,23 +6649,23 @@
       </c>
       <c r="T8" s="41"/>
       <c r="X8" s="6" t="str">
-        <f>'ใบงาน Agilent_JOBB6'!N9</f>
+        <f>'ใบงาน Agilent_JOB 6'!N9</f>
         <v>PO12345</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="6" customFormat="1" ht="13.5">
-      <c r="A9" s="75" t="s">
+    <row r="9" spans="1:26" s="6" customFormat="1" ht="13.8">
+      <c r="A9" s="193" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="75"/>
+      <c r="B9" s="193"/>
       <c r="C9" s="65"/>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
       <c r="F9" s="65"/>
-      <c r="G9" s="76"/>
-      <c r="H9" s="76"/>
-      <c r="I9" s="76"/>
-      <c r="J9" s="76"/>
+      <c r="G9" s="127"/>
+      <c r="H9" s="127"/>
+      <c r="I9" s="127"/>
+      <c r="J9" s="127"/>
       <c r="L9" s="18"/>
       <c r="M9" s="18"/>
       <c r="N9" s="18"/>
@@ -6671,33 +6673,33 @@
       <c r="P9" s="18"/>
       <c r="Q9" s="18"/>
       <c r="R9" s="18"/>
-      <c r="S9" s="77" t="s">
+      <c r="S9" s="113" t="s">
         <v>77</v>
       </c>
-      <c r="T9" s="77"/>
-      <c r="U9" s="77"/>
-      <c r="V9" s="77"/>
-    </row>
-    <row r="10" spans="1:26" s="6" customFormat="1" ht="13.5">
+      <c r="T9" s="113"/>
+      <c r="U9" s="113"/>
+      <c r="V9" s="113"/>
+    </row>
+    <row r="10" spans="1:26" s="6" customFormat="1" ht="13.8">
       <c r="A10" s="41" t="s">
         <v>221</v>
       </c>
       <c r="B10" s="18">
-        <f>'ใบงาน Agilent_JOBB6'!N8/50</f>
+        <f>'ใบงาน Agilent_JOB 6'!N8/50</f>
         <v>40</v>
       </c>
       <c r="C10" s="18"/>
-      <c r="D10" s="78" t="s">
+      <c r="D10" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="79" t="s">
+      <c r="E10" s="126"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
       <c r="K10" s="42"/>
       <c r="L10" s="18"/>
       <c r="M10" s="18"/>
@@ -6706,23 +6708,23 @@
       <c r="P10" s="18"/>
       <c r="Q10" s="18"/>
       <c r="R10" s="18"/>
-      <c r="S10" s="77"/>
-      <c r="T10" s="77"/>
-      <c r="U10" s="77"/>
-      <c r="V10" s="77"/>
-    </row>
-    <row r="11" spans="1:26" s="6" customFormat="1" ht="13.5">
-      <c r="B11" s="78"/>
+      <c r="S10" s="113"/>
+      <c r="T10" s="113"/>
+      <c r="U10" s="113"/>
+      <c r="V10" s="113"/>
+    </row>
+    <row r="11" spans="1:26" s="6" customFormat="1" ht="13.8">
+      <c r="B11" s="126"/>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
-      <c r="G11" s="79" t="s">
+      <c r="G11" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
       <c r="K11" s="18"/>
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
@@ -6734,21 +6736,21 @@
       <c r="S11" s="18"/>
       <c r="T11" s="18"/>
     </row>
-    <row r="12" spans="1:26" s="6" customFormat="1" ht="13.5">
+    <row r="12" spans="1:26" s="6" customFormat="1" ht="13.8">
       <c r="A12" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="78"/>
+      <c r="B12" s="126"/>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="79" t="s">
+      <c r="G12" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
+      <c r="H12" s="128"/>
+      <c r="I12" s="128"/>
+      <c r="J12" s="128"/>
       <c r="K12" s="18"/>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
@@ -6760,9 +6762,9 @@
       <c r="S12" s="18"/>
       <c r="T12" s="18"/>
     </row>
-    <row r="13" spans="1:26" s="6" customFormat="1" ht="13.5">
+    <row r="13" spans="1:26" s="6" customFormat="1" ht="13.8">
       <c r="A13" s="18"/>
-      <c r="B13" s="83"/>
+      <c r="B13" s="194"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
@@ -6782,348 +6784,348 @@
       <c r="S13" s="18"/>
       <c r="T13" s="18"/>
     </row>
-    <row r="14" spans="1:26" s="6" customFormat="1" ht="13.5">
-      <c r="A14" s="84" t="s">
+    <row r="14" spans="1:26" s="6" customFormat="1" ht="13.8">
+      <c r="A14" s="138" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="84" t="s">
+      <c r="B14" s="138" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="86" t="s">
+      <c r="C14" s="130" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="87"/>
-      <c r="G14" s="87"/>
-      <c r="H14" s="88"/>
-      <c r="I14" s="86" t="s">
+      <c r="D14" s="139"/>
+      <c r="E14" s="139"/>
+      <c r="F14" s="139"/>
+      <c r="G14" s="139"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="J14" s="87"/>
-      <c r="K14" s="87"/>
-      <c r="L14" s="87"/>
-      <c r="M14" s="87"/>
-      <c r="N14" s="88"/>
-      <c r="O14" s="86" t="s">
+      <c r="J14" s="139"/>
+      <c r="K14" s="139"/>
+      <c r="L14" s="139"/>
+      <c r="M14" s="139"/>
+      <c r="N14" s="140"/>
+      <c r="O14" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-      <c r="R14" s="96"/>
-      <c r="S14" s="96"/>
-      <c r="T14" s="97"/>
-      <c r="U14" s="101" t="s">
+      <c r="P14" s="131"/>
+      <c r="Q14" s="131"/>
+      <c r="R14" s="131"/>
+      <c r="S14" s="131"/>
+      <c r="T14" s="132"/>
+      <c r="U14" s="136" t="s">
         <v>82</v>
       </c>
-      <c r="V14" s="101"/>
-      <c r="W14" s="101"/>
-      <c r="X14" s="101"/>
-      <c r="Y14" s="101"/>
-      <c r="Z14" s="101"/>
-    </row>
-    <row r="15" spans="1:26" s="6" customFormat="1" ht="13.5">
-      <c r="A15" s="85"/>
-      <c r="B15" s="84"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="90"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="90"/>
-      <c r="K15" s="90"/>
-      <c r="L15" s="90"/>
-      <c r="M15" s="90"/>
-      <c r="N15" s="91"/>
-      <c r="O15" s="98"/>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="99"/>
-      <c r="R15" s="99"/>
-      <c r="S15" s="99"/>
-      <c r="T15" s="100"/>
-      <c r="U15" s="101"/>
-      <c r="V15" s="101"/>
-      <c r="W15" s="101"/>
-      <c r="X15" s="101"/>
-      <c r="Y15" s="101"/>
-      <c r="Z15" s="101"/>
-    </row>
-    <row r="16" spans="1:26" s="56" customFormat="1" ht="17.25">
-      <c r="A16" s="92">
+      <c r="V14" s="136"/>
+      <c r="W14" s="136"/>
+      <c r="X14" s="136"/>
+      <c r="Y14" s="136"/>
+      <c r="Z14" s="136"/>
+    </row>
+    <row r="15" spans="1:26" s="6" customFormat="1" ht="13.8">
+      <c r="A15" s="78"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="142"/>
+      <c r="E15" s="142"/>
+      <c r="F15" s="142"/>
+      <c r="G15" s="142"/>
+      <c r="H15" s="143"/>
+      <c r="I15" s="141"/>
+      <c r="J15" s="142"/>
+      <c r="K15" s="142"/>
+      <c r="L15" s="142"/>
+      <c r="M15" s="142"/>
+      <c r="N15" s="143"/>
+      <c r="O15" s="133"/>
+      <c r="P15" s="134"/>
+      <c r="Q15" s="134"/>
+      <c r="R15" s="134"/>
+      <c r="S15" s="134"/>
+      <c r="T15" s="135"/>
+      <c r="U15" s="136"/>
+      <c r="V15" s="136"/>
+      <c r="W15" s="136"/>
+      <c r="X15" s="136"/>
+      <c r="Y15" s="136"/>
+      <c r="Z15" s="136"/>
+    </row>
+    <row r="16" spans="1:26" s="56" customFormat="1" ht="17.399999999999999">
+      <c r="A16" s="144">
         <v>1</v>
       </c>
       <c r="B16" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="95"/>
-      <c r="K16" s="95"/>
-      <c r="L16" s="95"/>
-      <c r="M16" s="95"/>
-      <c r="N16" s="95"/>
-      <c r="O16" s="95"/>
-      <c r="P16" s="95"/>
-      <c r="Q16" s="95"/>
-      <c r="R16" s="95"/>
-      <c r="S16" s="95"/>
-      <c r="T16" s="95"/>
-      <c r="U16" s="95"/>
-      <c r="V16" s="95"/>
-      <c r="W16" s="95"/>
-      <c r="X16" s="95"/>
-      <c r="Y16" s="95"/>
-      <c r="Z16" s="95"/>
-    </row>
-    <row r="17" spans="1:26" s="56" customFormat="1" ht="17.25">
-      <c r="A17" s="93"/>
+      <c r="C16" s="137"/>
+      <c r="D16" s="137"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="137"/>
+      <c r="G16" s="137"/>
+      <c r="H16" s="137"/>
+      <c r="I16" s="137"/>
+      <c r="J16" s="137"/>
+      <c r="K16" s="137"/>
+      <c r="L16" s="137"/>
+      <c r="M16" s="137"/>
+      <c r="N16" s="137"/>
+      <c r="O16" s="137"/>
+      <c r="P16" s="137"/>
+      <c r="Q16" s="137"/>
+      <c r="R16" s="137"/>
+      <c r="S16" s="137"/>
+      <c r="T16" s="137"/>
+      <c r="U16" s="137"/>
+      <c r="V16" s="137"/>
+      <c r="W16" s="137"/>
+      <c r="X16" s="137"/>
+      <c r="Y16" s="137"/>
+      <c r="Z16" s="137"/>
+    </row>
+    <row r="17" spans="1:26" s="56" customFormat="1" ht="17.399999999999999">
+      <c r="A17" s="145"/>
       <c r="B17" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="95"/>
-      <c r="K17" s="95"/>
-      <c r="L17" s="95"/>
-      <c r="M17" s="95"/>
-      <c r="N17" s="95"/>
-      <c r="O17" s="95"/>
-      <c r="P17" s="95"/>
-      <c r="Q17" s="95"/>
-      <c r="R17" s="95"/>
-      <c r="S17" s="95"/>
-      <c r="T17" s="95"/>
-      <c r="U17" s="95"/>
-      <c r="V17" s="95"/>
-      <c r="W17" s="95"/>
-      <c r="X17" s="95"/>
-      <c r="Y17" s="95"/>
-      <c r="Z17" s="95"/>
-    </row>
-    <row r="18" spans="1:26" s="56" customFormat="1" ht="17.25">
-      <c r="A18" s="93"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
+      <c r="H17" s="137"/>
+      <c r="I17" s="137"/>
+      <c r="J17" s="137"/>
+      <c r="K17" s="137"/>
+      <c r="L17" s="137"/>
+      <c r="M17" s="137"/>
+      <c r="N17" s="137"/>
+      <c r="O17" s="137"/>
+      <c r="P17" s="137"/>
+      <c r="Q17" s="137"/>
+      <c r="R17" s="137"/>
+      <c r="S17" s="137"/>
+      <c r="T17" s="137"/>
+      <c r="U17" s="137"/>
+      <c r="V17" s="137"/>
+      <c r="W17" s="137"/>
+      <c r="X17" s="137"/>
+      <c r="Y17" s="137"/>
+      <c r="Z17" s="137"/>
+    </row>
+    <row r="18" spans="1:26" s="56" customFormat="1" ht="17.399999999999999">
+      <c r="A18" s="145"/>
       <c r="B18" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="95"/>
-      <c r="K18" s="95"/>
-      <c r="L18" s="95"/>
-      <c r="M18" s="95"/>
-      <c r="N18" s="95"/>
-      <c r="O18" s="95"/>
-      <c r="P18" s="95"/>
-      <c r="Q18" s="95"/>
-      <c r="R18" s="95"/>
-      <c r="S18" s="95"/>
-      <c r="T18" s="95"/>
-      <c r="U18" s="95"/>
-      <c r="V18" s="95"/>
-      <c r="W18" s="95"/>
-      <c r="X18" s="95"/>
-      <c r="Y18" s="95"/>
-      <c r="Z18" s="95"/>
-    </row>
-    <row r="19" spans="1:26" s="56" customFormat="1" ht="17.25">
-      <c r="A19" s="93"/>
+      <c r="C18" s="137"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="137"/>
+      <c r="G18" s="137"/>
+      <c r="H18" s="137"/>
+      <c r="I18" s="137"/>
+      <c r="J18" s="137"/>
+      <c r="K18" s="137"/>
+      <c r="L18" s="137"/>
+      <c r="M18" s="137"/>
+      <c r="N18" s="137"/>
+      <c r="O18" s="137"/>
+      <c r="P18" s="137"/>
+      <c r="Q18" s="137"/>
+      <c r="R18" s="137"/>
+      <c r="S18" s="137"/>
+      <c r="T18" s="137"/>
+      <c r="U18" s="137"/>
+      <c r="V18" s="137"/>
+      <c r="W18" s="137"/>
+      <c r="X18" s="137"/>
+      <c r="Y18" s="137"/>
+      <c r="Z18" s="137"/>
+    </row>
+    <row r="19" spans="1:26" s="56" customFormat="1" ht="17.399999999999999">
+      <c r="A19" s="145"/>
       <c r="B19" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="95"/>
-      <c r="K19" s="95"/>
-      <c r="L19" s="95"/>
-      <c r="M19" s="95"/>
-      <c r="N19" s="95"/>
-      <c r="O19" s="95"/>
-      <c r="P19" s="95"/>
-      <c r="Q19" s="95"/>
-      <c r="R19" s="95"/>
-      <c r="S19" s="95"/>
-      <c r="T19" s="95"/>
-      <c r="U19" s="95"/>
-      <c r="V19" s="95"/>
-      <c r="W19" s="95"/>
-      <c r="X19" s="95"/>
-      <c r="Y19" s="95"/>
-      <c r="Z19" s="95"/>
-    </row>
-    <row r="20" spans="1:26" s="56" customFormat="1" ht="17.25">
-      <c r="A20" s="94"/>
+      <c r="C19" s="137"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="137"/>
+      <c r="G19" s="137"/>
+      <c r="H19" s="137"/>
+      <c r="I19" s="137"/>
+      <c r="J19" s="137"/>
+      <c r="K19" s="137"/>
+      <c r="L19" s="137"/>
+      <c r="M19" s="137"/>
+      <c r="N19" s="137"/>
+      <c r="O19" s="137"/>
+      <c r="P19" s="137"/>
+      <c r="Q19" s="137"/>
+      <c r="R19" s="137"/>
+      <c r="S19" s="137"/>
+      <c r="T19" s="137"/>
+      <c r="U19" s="137"/>
+      <c r="V19" s="137"/>
+      <c r="W19" s="137"/>
+      <c r="X19" s="137"/>
+      <c r="Y19" s="137"/>
+      <c r="Z19" s="137"/>
+    </row>
+    <row r="20" spans="1:26" s="56" customFormat="1" ht="17.399999999999999">
+      <c r="A20" s="146"/>
       <c r="B20" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="95"/>
-      <c r="D20" s="95"/>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="95"/>
-      <c r="I20" s="95"/>
-      <c r="J20" s="95"/>
-      <c r="K20" s="95"/>
-      <c r="L20" s="95"/>
-      <c r="M20" s="95"/>
-      <c r="N20" s="95"/>
-      <c r="O20" s="95"/>
-      <c r="P20" s="95"/>
-      <c r="Q20" s="95"/>
-      <c r="R20" s="95"/>
-      <c r="S20" s="95"/>
-      <c r="T20" s="95"/>
-      <c r="U20" s="95"/>
-      <c r="V20" s="95"/>
-      <c r="W20" s="95"/>
-      <c r="X20" s="95"/>
-      <c r="Y20" s="95"/>
-      <c r="Z20" s="95"/>
-    </row>
-    <row r="21" spans="1:26" s="56" customFormat="1" ht="17.25">
+      <c r="C20" s="137"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="137"/>
+      <c r="G20" s="137"/>
+      <c r="H20" s="137"/>
+      <c r="I20" s="137"/>
+      <c r="J20" s="137"/>
+      <c r="K20" s="137"/>
+      <c r="L20" s="137"/>
+      <c r="M20" s="137"/>
+      <c r="N20" s="137"/>
+      <c r="O20" s="137"/>
+      <c r="P20" s="137"/>
+      <c r="Q20" s="137"/>
+      <c r="R20" s="137"/>
+      <c r="S20" s="137"/>
+      <c r="T20" s="137"/>
+      <c r="U20" s="137"/>
+      <c r="V20" s="137"/>
+      <c r="W20" s="137"/>
+      <c r="X20" s="137"/>
+      <c r="Y20" s="137"/>
+      <c r="Z20" s="137"/>
+    </row>
+    <row r="21" spans="1:26" s="56" customFormat="1" ht="17.399999999999999">
       <c r="A21" s="54">
         <v>2</v>
       </c>
       <c r="B21" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="95"/>
-      <c r="D21" s="95"/>
-      <c r="E21" s="95"/>
-      <c r="F21" s="95"/>
-      <c r="G21" s="95"/>
-      <c r="H21" s="95"/>
-      <c r="I21" s="95"/>
-      <c r="J21" s="95"/>
-      <c r="K21" s="95"/>
-      <c r="L21" s="95"/>
-      <c r="M21" s="95"/>
-      <c r="N21" s="95"/>
-      <c r="O21" s="95"/>
-      <c r="P21" s="95"/>
-      <c r="Q21" s="95"/>
-      <c r="R21" s="95"/>
-      <c r="S21" s="95"/>
-      <c r="T21" s="95"/>
-      <c r="U21" s="95"/>
-      <c r="V21" s="95"/>
-      <c r="W21" s="95"/>
-      <c r="X21" s="95"/>
-      <c r="Y21" s="95"/>
-      <c r="Z21" s="95"/>
-    </row>
-    <row r="22" spans="1:26" s="56" customFormat="1" ht="17.25">
+      <c r="C21" s="137"/>
+      <c r="D21" s="137"/>
+      <c r="E21" s="137"/>
+      <c r="F21" s="137"/>
+      <c r="G21" s="137"/>
+      <c r="H21" s="137"/>
+      <c r="I21" s="137"/>
+      <c r="J21" s="137"/>
+      <c r="K21" s="137"/>
+      <c r="L21" s="137"/>
+      <c r="M21" s="137"/>
+      <c r="N21" s="137"/>
+      <c r="O21" s="137"/>
+      <c r="P21" s="137"/>
+      <c r="Q21" s="137"/>
+      <c r="R21" s="137"/>
+      <c r="S21" s="137"/>
+      <c r="T21" s="137"/>
+      <c r="U21" s="137"/>
+      <c r="V21" s="137"/>
+      <c r="W21" s="137"/>
+      <c r="X21" s="137"/>
+      <c r="Y21" s="137"/>
+      <c r="Z21" s="137"/>
+    </row>
+    <row r="22" spans="1:26" s="56" customFormat="1" ht="17.399999999999999">
       <c r="A22" s="54">
         <v>3</v>
       </c>
       <c r="B22" s="55" t="s">
         <v>223</v>
       </c>
-      <c r="C22" s="95"/>
-      <c r="D22" s="95"/>
-      <c r="E22" s="95"/>
-      <c r="F22" s="95"/>
-      <c r="G22" s="95"/>
-      <c r="H22" s="95"/>
-      <c r="I22" s="95"/>
-      <c r="J22" s="95"/>
-      <c r="K22" s="95"/>
-      <c r="L22" s="95"/>
-      <c r="M22" s="95"/>
-      <c r="N22" s="95"/>
-      <c r="O22" s="95"/>
-      <c r="P22" s="95"/>
-      <c r="Q22" s="95"/>
-      <c r="R22" s="95"/>
-      <c r="S22" s="95"/>
-      <c r="T22" s="95"/>
-      <c r="U22" s="95"/>
-      <c r="V22" s="95"/>
-      <c r="W22" s="95"/>
-      <c r="X22" s="95"/>
-      <c r="Y22" s="95"/>
-      <c r="Z22" s="95"/>
-    </row>
-    <row r="23" spans="1:26" s="56" customFormat="1" ht="17.25">
+      <c r="C22" s="137"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="137"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="137"/>
+      <c r="I22" s="137"/>
+      <c r="J22" s="137"/>
+      <c r="K22" s="137"/>
+      <c r="L22" s="137"/>
+      <c r="M22" s="137"/>
+      <c r="N22" s="137"/>
+      <c r="O22" s="137"/>
+      <c r="P22" s="137"/>
+      <c r="Q22" s="137"/>
+      <c r="R22" s="137"/>
+      <c r="S22" s="137"/>
+      <c r="T22" s="137"/>
+      <c r="U22" s="137"/>
+      <c r="V22" s="137"/>
+      <c r="W22" s="137"/>
+      <c r="X22" s="137"/>
+      <c r="Y22" s="137"/>
+      <c r="Z22" s="137"/>
+    </row>
+    <row r="23" spans="1:26" s="56" customFormat="1" ht="17.399999999999999">
       <c r="A23" s="54">
         <v>4</v>
       </c>
       <c r="B23" s="55" t="s">
         <v>224</v>
       </c>
-      <c r="C23" s="95"/>
-      <c r="D23" s="95"/>
-      <c r="E23" s="95"/>
-      <c r="F23" s="95"/>
-      <c r="G23" s="95"/>
-      <c r="H23" s="95"/>
-      <c r="I23" s="95"/>
-      <c r="J23" s="95"/>
-      <c r="K23" s="95"/>
-      <c r="L23" s="95"/>
-      <c r="M23" s="95"/>
-      <c r="N23" s="95"/>
-      <c r="O23" s="95"/>
-      <c r="P23" s="95"/>
-      <c r="Q23" s="95"/>
-      <c r="R23" s="95"/>
-      <c r="S23" s="95"/>
-      <c r="T23" s="95"/>
-      <c r="U23" s="95"/>
-      <c r="V23" s="95"/>
-      <c r="W23" s="95"/>
-      <c r="X23" s="95"/>
-      <c r="Y23" s="95"/>
-      <c r="Z23" s="95"/>
-    </row>
-    <row r="24" spans="1:26" s="6" customFormat="1" ht="13.5">
+      <c r="C23" s="137"/>
+      <c r="D23" s="137"/>
+      <c r="E23" s="137"/>
+      <c r="F23" s="137"/>
+      <c r="G23" s="137"/>
+      <c r="H23" s="137"/>
+      <c r="I23" s="137"/>
+      <c r="J23" s="137"/>
+      <c r="K23" s="137"/>
+      <c r="L23" s="137"/>
+      <c r="M23" s="137"/>
+      <c r="N23" s="137"/>
+      <c r="O23" s="137"/>
+      <c r="P23" s="137"/>
+      <c r="Q23" s="137"/>
+      <c r="R23" s="137"/>
+      <c r="S23" s="137"/>
+      <c r="T23" s="137"/>
+      <c r="U23" s="137"/>
+      <c r="V23" s="137"/>
+      <c r="W23" s="137"/>
+      <c r="X23" s="137"/>
+      <c r="Y23" s="137"/>
+      <c r="Z23" s="137"/>
+    </row>
+    <row r="24" spans="1:26" s="6" customFormat="1" ht="13.8">
       <c r="A24" s="7"/>
-      <c r="C24" s="102"/>
-      <c r="D24" s="102"/>
-      <c r="E24" s="102"/>
-      <c r="F24" s="102"/>
+      <c r="C24" s="147"/>
+      <c r="D24" s="147"/>
+      <c r="E24" s="147"/>
+      <c r="F24" s="147"/>
     </row>
     <row r="25" spans="1:26" s="58" customFormat="1" ht="15">
       <c r="A25" s="59"/>
-      <c r="L25" s="103"/>
-      <c r="M25" s="103"/>
-    </row>
-    <row r="26" spans="1:26" s="6" customFormat="1" ht="13.5">
+      <c r="L25" s="152"/>
+      <c r="M25" s="152"/>
+    </row>
+    <row r="26" spans="1:26" s="6" customFormat="1" ht="13.8">
       <c r="A26" s="7"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="102"/>
-    </row>
-    <row r="27" spans="1:26" s="6" customFormat="1" ht="13.5">
+      <c r="L26" s="147"/>
+      <c r="M26" s="147"/>
+    </row>
+    <row r="27" spans="1:26" s="6" customFormat="1" ht="13.8">
       <c r="A27" s="7"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="102"/>
-    </row>
-    <row r="28" spans="1:26" s="6" customFormat="1" ht="13.5">
+      <c r="L27" s="147"/>
+      <c r="M27" s="147"/>
+    </row>
+    <row r="28" spans="1:26" s="6" customFormat="1" ht="13.8">
       <c r="A28" s="7"/>
-      <c r="L28" s="102"/>
-      <c r="M28" s="102"/>
+      <c r="L28" s="147"/>
+      <c r="M28" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="58">
@@ -7132,6 +7134,9 @@
     <mergeCell ref="L27:M27"/>
     <mergeCell ref="L28:M28"/>
     <mergeCell ref="W7:Z7"/>
+    <mergeCell ref="O14:T15"/>
+    <mergeCell ref="U14:Z15"/>
+    <mergeCell ref="U17:Z17"/>
     <mergeCell ref="C23:H23"/>
     <mergeCell ref="I23:N23"/>
     <mergeCell ref="O23:T23"/>
@@ -7145,13 +7150,6 @@
     <mergeCell ref="I22:N22"/>
     <mergeCell ref="O22:T22"/>
     <mergeCell ref="U22:Z22"/>
-    <mergeCell ref="O14:T15"/>
-    <mergeCell ref="U14:Z15"/>
-    <mergeCell ref="U17:Z17"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="I18:N18"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="U18:Z18"/>
     <mergeCell ref="A16:A20"/>
     <mergeCell ref="C16:H16"/>
     <mergeCell ref="I16:N16"/>
@@ -7171,6 +7169,10 @@
     <mergeCell ref="B11:B13"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="G12:J12"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="I18:N18"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="U18:Z18"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:H15"/>
